--- a/scripts/productos-digitales/guia-chocolateria/build/capacidad-obrador-y-clima.xlsx
+++ b/scripts/productos-digitales/guia-chocolateria/build/capacidad-obrador-y-clima.xlsx
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx!Apertura del Negocio</t>
+          <t>kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx, hoja «Apertura del Negocio»</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>kit-tareas-chocolateria/01-apertura-cierre.xlsx!Apertura</t>
+          <t>kit-tareas-chocolateria/01-apertura-cierre.xlsx, hoja «Apertura»</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -2313,7 +2313,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>kit-tareas-chocolateria/01-apertura-cierre.xlsx!Apertura</t>
+          <t>kit-tareas-chocolateria/01-apertura-cierre.xlsx, hoja «Apertura»</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -2343,7 +2343,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>kit-tareas-chocolateria/01-apertura-cierre.xlsx!Apertura</t>
+          <t>kit-tareas-chocolateria/01-apertura-cierre.xlsx, hoja «Apertura»</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx!Apertura del Negocio</t>
+          <t>kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx, hoja «Apertura del Negocio»</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">

--- a/scripts/productos-digitales/guia-chocolateria/build/capacidad-obrador-y-clima.xlsx
+++ b/scripts/productos-digitales/guia-chocolateria/build/capacidad-obrador-y-clima.xlsx
@@ -699,7 +699,7 @@
     <row r="7" ht="68" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2. Hoja «Zonas y m2»: reparte los metros entre las seis zonas y numera el recorrido de la marcha adelante, del 1 al 6. La hoja te dice si el reparto cuadra con la superficie declarada, qué parte del local es producción y si el recorrido tiene un cruce.</t>
+          <t>2. Hoja «Zonas y m²»: reparte los metros entre las seis zonas y numera el recorrido de la marcha adelante, del 1 al 6. La hoja te dice si el reparto cuadra con la superficie declarada, qué parte del local es producción y si el recorrido tiene un cruce.</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
     <row r="19" ht="74" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>EL CLIMA NO ES CONFORT: ES LA PARTIDA QUE DECIDE SI LA COBERTURA CRISTALIZA. 18-20 grados C y 50-60 % de humedad en el obrador, y una cámara a 15-18 grados C que no es una nevera. Este libro no calcula tu carga térmica -no hay un solo coeficiente publicado y verificable para hacerlo- pero sí comprueba que lo que quieres, el agosto de tu ciudad y lo que te ofrecen son coherentes entre sí, y te da la lista de preguntas que hay que hacerle al instalador.</t>
+          <t>EL CLIMA NO ES CONFORT: ES LA PARTIDA QUE DECIDE SI LA COBERTURA CRISTALIZA. 18-20 °C y 50-60 % de humedad en el obrador, y una cámara a 15-18 °C que no es una nevera. Este libro no calcula tu carga térmica -no hay un solo coeficiente publicado y verificable para hacerlo- pero sí comprueba que lo que quieres, el agosto de tu ciudad y lo que te ofrecen son coherentes entre sí, y te da la lista de preguntas que hay que hacerle al instalador.</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Parte de la jornada que se pasa a pie de mesa. El 15 % restante es recepcion, limpieza, formacion y reuniones.</t>
+          <t>Parte de la jornada que se pasa a pie de mesa. El 15 % restante es recepción, limpieza, formación y reuniones.</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>6 dias por semana x 52 semanas = 312, menos 8 dias de cierre por festivos = 304. En agosto la TIENDA NO CIERRA: lo que para es el obrador (D36, y el literal del kit dice «la tienda abre para el turista aunque el obrador pare»). Una bomboneria de menos de 300 m2 tiene libertad horaria por el art. 5.2 de la Ley 1/2004, no por el 5.1 (`CHN-77`).</t>
+          <t>6 días por semana x 52 semanas = 312, menos 8 días de cierre por festivos = 304. En agosto la TIENDA NO CIERRA: lo que para es el obrador (D36, y el literal del kit dice «la tienda abre para el turista aunque el obrador pare»). Una bombonería de menos de 300 m² tiene libertad horaria por el art. 5.2 de la Ley 1/2004, no por el 5.1 (`CHN-77`).</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Supuesto declarado, elegido por convergencia de cuatro fuentes CON SU FORMATO DICHO: `CHS-03` (bomboneria artesana, 60-100 m2), `CHS-38a` (pasteleria-bomboneria con obrador, 90 m2 y 26.000 euros de traspaso: el comparable mas cercano del censo), `CHS-58` (minimo de franquicia, 55 m2) y, como referencia de OTRO formato, los traspasos de churreria-chocolateria `CHS-37a` (75 m2) y `CHS-37b` (74 m2). Se elige 75 por estar dentro de `CHS-03` y por debajo de `CHS-38a`. El reparto por zona tambien es supuesto.</t>
+          <t>Supuesto declarado, elegido por convergencia de cuatro fuentes CON SU FORMATO DICHO: `CHS-03` (bombonería artesana, 60-100 m²), `CHS-38a` (pasteleria-bomboneria con obrador, 90 m² y 26.000 euros de traspaso: el comparable mas cercano del censo), `CHS-58` (mínimo de franquicia, 55 m²) y, como referencia de OTRO formato, los traspasos de churreria-chocolateria `CHS-37a` (75 m²) y `CHS-37b` (74 m²). Se elige 75 por estar dentro de `CHS-03` y por debajo de `CHS-38a`. El reparto por zona también es supuesto.</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Supuesto. Un obrador de chocolate NO tiene hornos: lo que consume es el frio (camara, nevera de rellenos y vitrina, 24 horas), la climatizacion con deshumidificacion y la atemperadora. La potencia a contratar la fija el proyecto electrico, no una tabla: el libro 1 la pide en celda verde.</t>
+          <t>Supuesto. Un obrador de chocolate NO tiene hornos: lo que consume es el frío (cámara, nevera de rellenos y vitrina, 24 horas), la climatización con deshumidificación y la atemperadora. La potencia a contratar la fija el proyecto eléctrico, no una tabla: el libro 1 la pide en celda verde.</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Supuesto de ciudad media espanola de interior en agosto. Es una CELDA VERDE del libro 1: el lector pone la de su ciudad, y con ella el semaforo compara la temperatura objetivo del obrador con la potencia frigorifica que le OFREZCA EL INSTALADOR. El libro NO calcula carga termica (D33): no hay un solo coeficiente con fuente.</t>
+          <t>Supuesto de ciudad media española de interior en agosto. Es una CELDA VERDE del libro 1: el lector pone la de su ciudad, y con ella el semáforo compara la temperatura objetivo del obrador con la potencia frigorífica que le OFREZCA EL INSTALADOR. El libro NO calcula carga térmica (D33): no hay un solo coeficiente con fuente.</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Ningún ayuntamiento puede exigirte licencia previa de instalación, de funcionamiento o de actividad hasta 750 m2 de superficie útil de exposición y venta al público, porque el epígrafe 644.5 «Comercio al por menor de bombones y caramelos» está en el Anexo de la Ley 12/2012. OJO: la chocolatería de TAZA (grupo 676) NO está en ese Anexo (`CHN-49c`), así que la variante de taza y churros no se libra.</t>
+          <t>Ningún ayuntamiento puede exigirte licencia previa de instalación, de funcionamiento o de actividad hasta 750 m² de superficie útil de exposición y venta al público, porque el epígrafe 644.5 «Comercio al por menor de bombones y caramelos» está en el Anexo de la Ley 12/2012. OJO: la chocolatería de TAZA (grupo 676) NO está en ese Anexo (`CHN-49c`), así que la variante de taza y churros no se libra.</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
     <row r="26" ht="48" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Los valores marcados «supuesto» son los de la bombonería de ejemplo «La Almendra» (75 m2, 45 de producción y 22 de tienda, un turno, tres personas y 2,5 jornadas). NO son datos de sector: son un punto de partida coherente para que puedas ver el libro funcionando antes de meter los tuyos.</t>
+          <t>Los valores marcados «supuesto» son los de la bombonería de ejemplo «La Almendra» (75 m², 45 de producción y 22 de tienda, un turno, tres personas y 2,5 jornadas). NO son datos de sector: son un punto de partida coherente para que puedas ver el libro funcionando antes de meter los tuyos.</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Produccion</t>
+          <t>Producción</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>La zona que manda sobre el local: aqui van la atemperadora, la mesa de marmol o granito, la enrobadora y los moldes. Clima propio (18-20 grados C y 50-60 % de humedad, F_KIT_08_APERTURA) y marcha adelante: la cobertura entra por un extremo y el bombon acabado sale por el otro sin cruzarse con ella.</t>
+          <t>La zona que manda sobre el local: aquí van la atemperadora, la mesa de mármol o granito, la enrobadora y los moldes. Clima propio (18-20 °C y 50-60 % de humedad, kit-tareas-chocolateria/08-apertura-cierre-negocio.xlsx, hoja «Apertura del Negocio») y marcha adelante: la cobertura entra por un extremo y el bombón acabado sale por el otro sin cruzarse con ella.</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Camara de chocolate</t>
+          <t>Cámara de chocolate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Produccion</t>
+          <t>Producción</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Zona propia y climatizada a 15-18 grados C con 50-60 % de humedad (F_KIT_01_APERTURA). No es una nevera: el chocolate acabado NO va a 4 grados C. Dentro de ella, o al lado, la nevera de rellenos y ganaches a 0-4 grados C.</t>
+          <t>Zona propia y climatizada a 15-18 °C con 50-60 % de humedad (kit-tareas-chocolateria/01-apertura-cierre.xlsx, hoja «Apertura»). No es una nevera: el chocolate acabado NO va a 4 °C. Dentro de ella, o al lado, la nevera de rellenos y ganaches a 0-4 °C.</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Almacen de cobertura y materias primas</t>
+          <t>Almacén de cobertura y materias primas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Produccion</t>
+          <t>Producción</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>La cobertura llega en cajas de 5 a 25 kg y es el inmovilizado mas grande del obrador: el libro 3 calcula cuantas semanas de stock caben aqui. En oscuridad y lejos de olores fuertes: el cacao los absorbe (F_KIT_MOLDEADO).</t>
+          <t>La cobertura llega en cajas de 5 a 25 kg y es el inmovilizado más grande del obrador: el libro 3 calcula cuántas semanas de stock caben aquí. En oscuridad y lejos de olores fuertes: el cacao los absorbe (kit-tareas-chocolateria/02-partidas-produccion.xlsx, hoja «Moldeado»).</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Produccion</t>
+          <t>Producción</t>
         </is>
       </c>
       <c r="D9" s="8" t="n">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Mesa de montaje de cajas, etiquetadora y almacen de packaging de campana. Es la zona que se desborda en Navidad y la que nadie dibuja en el plano.</t>
+          <t>Mesa de montaje de cajas, etiquetadora y almacén de packaging de campaña. Es la zona que se desborda en Navidad y la que nadie dibuja en el plano.</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Sala a 20-22 grados C (F_KIT_01_APERTURA) con la vitrina de bomboneria a 16-18 grados C. Los dos climas son distintos y conviven en la misma sala: es el motivo de que la vitrina lleve su propio control.</t>
+          <t>Sala a 20-22 °C (kit-tareas-chocolateria/01-apertura-cierre.xlsx, hoja «Apertura») con la vitrina de bombonería a 16-18 °C. Los dos climas son distintos y conviven en la misma sala: es el motivo de que la vitrina lleve su propio control.</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Vestuario de personal separado del aseo de publico. Si no caben los dos, el local no sirve: es una de las eliminatorias de la ficha de visita.</t>
+          <t>Vestuario de personal separado del aseo de público. Si no caben los dos, el local no sirve: es una de las eliminatorias de la ficha de visita.</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Descuadre (m2)</t>
+          <t>Descuadre (m²)</t>
         </is>
       </c>
       <c r="D15" s="16">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="D17" s="16">
-        <f>SUMIF(C6:C11,"Produccion",D6:D11)</f>
+        <f>SUMIF(C6:C11,"Producción",D6:D11)</f>
         <v>45.0</v>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Es la superficie que se compara con los 750 m2 de la Ley 12/2012 en la ficha de visita: la de EXPOSICIÓN Y VENTA al público, no la del local entero.</t>
+          <t>Es la superficie que se compara con los 750 m² de la Ley 12/2012 en la ficha de visita: la de EXPOSICIÓN Y VENTA al público, no la del local entero.</t>
         </is>
       </c>
     </row>
@@ -2254,19 +2254,19 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Verificar la temperatura y la humedad del obrador: objetivo 18-20 grados C y 50-60 %</t>
+          <t>Verificar la temperatura y la humedad del obrador: objetivo 18-20 °C y 50-60 %</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Es la tarea 17 de la hoja, y es el objetivo mas restrictivo que publica el kit: es el que manda. `CHS-44` publica 18-22 grados C como rango de trabajo de un tercero, y entra en la prosa del cap. 07 como tal, nunca como objetivo del juego de datos.</t>
+          <t>Es la tarea 17 de la hoja, y es el objetivo mas restrictivo que publica el kit: es el que manda. `CHS-44` publica 18-22 °C como rango de trabajo de un tercero, y entra en la prosa del cap. 07 como tal, nunca como objetivo del juego de datos.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Camara de conservacion de chocolate</t>
+          <t>Cámara de conservación de chocolate</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Comprobar que la camara de conservacion ha funcionado toda la noche (sin cortes ni alarmas) y registrar la temperatura: objetivo 15-18 grados C y 50-60 % de humedad</t>
+          <t>Comprobar que la cámara de conservación ha funcionado toda la noche (sin cortes ni alarmas) y registrar la temperatura: objetivo 15-18 °C y 50-60 % de humedad</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Tarea 2. Es la misma ventana en la que el kit declara las vidas utiles.</t>
+          <t>Tarea 2. Es la misma ventana en la que el kit declara las vidas útiles.</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Comprobar que la nevera de rellenos y ganaches ha funcionado toda la noche y registrar la temperatura: objetivo 0-4 grados C</t>
+          <t>Comprobar que la nevera de rellenos y ganaches ha funcionado toda la noche y registrar la temperatura: objetivo 0-4 °C</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Tarea 3. Es la nevera del RELLENO, no la del bombon acabado: el chocolate terminado no va a 4 grados C, condensa.</t>
+          <t>Tarea 3. Es la nevera del RELLENO, no la del bombón acabado: el chocolate terminado no va a 4 °C, condensa.</t>
         </is>
       </c>
     </row>
@@ -2348,19 +2348,19 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Encender aire acondicionado - mantener sala 20-22 grados C</t>
+          <t>Encender aire acondicionado - mantener sala 20-22 °C</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Tarea 6. Confundir la temperatura de la SALA con la de la CAMARA es uno de los errores de metodo que la SPEC prohibe: son dos cosas distintas y conviven en el mismo local.</t>
+          <t>Tarea 6. Confundir la temperatura de la SALA con la de la CÁMARA es uno de los errores de método que la SPEC prohíbe: son dos cosas distintas y conviven en el mismo local.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Vitrina de bomboneria</t>
+          <t>Vitrina de bombonería</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Comprobar que las vitrinas temperadas han alcanzado 16-18 grados C y menos del 55 % de humedad antes de montar el genero</t>
+          <t>Comprobar que las vitrinas temperadas han alcanzado 16-18 °C y menos del 55 % de humedad antes de montar el genero</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Tarea 16. Es el OBJETIVO OPERATIVO, lo que se comprueba cada manana. `CHS-43` publica ademas el RANGO DE TRABAJO de un equipo real (+14/+17 grados C, Docriluc WB-6-6-R, base SIN IVA declarada), que es otra cosa. El semaforo del libro 5 se alimenta del rango que el lector teclea y solo avisa por encima de 20 grados C.</t>
+          <t>Tarea 16. Es el OBJETIVO OPERATIVO, lo que se comprueba cada mañana. `CHS-43` publica además el RANGO DE TRABAJO de un equipo real (+14/+17 °C, Docriluc WB-6-6-R, base SIN IVA declarada), que es otra cosa. El semáforo del libro 5 se alimenta del rango que el lector teclea y solo avisa por encima de 20 °C.</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>La nevera es la del RELLENO, a 0-4 grados C. El bombón acabado NO va a 4 grados C: condensa, y el agua de la condensación disuelve el azúcar de la superficie.</t>
+          <t>La nevera es la del RELLENO, a 0-4 °C. El bombón acabado NO va a 4 °C: condensa, y el agua de la condensación disuelve el azúcar de la superficie.</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>NO ES UN CRITERIO DE DIMENSIONADO Y POR ESO NO LLEVA SEMÁFORO: es tu propia oferta dividida entre tus propios metros. Sirve para una sola cosa, y es útil: enseñársela al segundo instalador y preguntarle por qué la suya se parece o no se parece. Cualquier tabla que te diga «tantos kW por m2 de obrador de chocolate» está inventada.</t>
+          <t>NO ES UN CRITERIO DE DIMENSIONADO Y POR ESO NO LLEVA SEMÁFORO: es tu propia oferta dividida entre tus propios metros. Sirve para una sola cosa, y es útil: enseñársela al segundo instalador y preguntarle por qué la suya se parece o no se parece. Cualquier tabla que te diga «tantos kW por m² de obrador de chocolate» está inventada.</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2659,7 @@
     <row r="37" ht="52" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>¿Qué volumen en m3 has tomado para el obrador?</t>
+          <t>¿Qué volumen en m³ has tomado para el obrador?</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Los metros cuadrados de la hoja «Zonas y m2» por la altura libre. Si el número que ha usado no se parece al tuyo, ha dimensionado otro local.</t>
+          <t>Los metros cuadrados de la hoja «Zonas y m²» por la altura libre. Si el número que ha usado no se parece al tuyo, ha dimensionado otro local.</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Es LA pregunta. Un equipo dimensionado para un salto de 10 grados no sostiene 18-20 grados C dentro con 36 fuera, y en agosto es cuando se nota.</t>
+          <t>Es LA pregunta. Un equipo dimensionado para un salto de 10 grados no sostiene 18-20 °C dentro con 36 fuera, y en agosto es cuando se nota.</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
     <row r="59" ht="90" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>POR QUÉ ESTA HOJA NO CALCULA TU CARGA TÉRMICA. Para calcularla harían falta la transmitancia de cada cerramiento de TU local, un coeficiente por m3, los aportes internos reales y las renovaciones de aire, y no existe ninguna fuente publicada y verificable que dé esos números para un obrador de chocolate. Las dos salidas fáciles estaban prohibidas: inventarse los coeficientes, o dejarte celdas verdes que no sabrías rellenar. Lo que sí puede hacer un libro honesto es lo de esta hoja: comprobar que las tres cifras que tú sí conoces encajan entre sí, y ponerte delante las diez preguntas que separan un presupuesto de una conversación. Si tu instalador no contesta a las diez por escrito, no tienes una oferta: tienes un precio.</t>
+          <t>POR QUÉ ESTA HOJA NO CALCULA TU CARGA TÉRMICA. Para calcularla harían falta la transmitancia de cada cerramiento de TU local, un coeficiente por m³, los aportes internos reales y las renovaciones de aire, y no existe ninguna fuente publicada y verificable que dé esos números para un obrador de chocolate. Las dos salidas fáciles estaban prohibidas: inventarse los coeficientes, o dejarte celdas verdes que no sabrías rellenar. Lo que sí puede hacer un libro honesto es lo de esta hoja: comprobar que las tres cifras que tú sí conoces encajan entre sí, y ponerte delante las diez preguntas que separan un presupuesto de una conversación. Si tu instalador no contesta a las diez por escrito, no tienes una oferta: tienes un precio.</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cámara climatizada de chocolate, unos 6 m2</t>
+          <t>Cámara climatizada de chocolate, unos 6 m²</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>m3 útiles por rotación</t>
+          <t>m³ útiles por rotación</t>
         </is>
       </c>
       <c r="G13" s="8" t="n">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>Aquí el «ciclo» es una rotación de la cámara. NO es una nevera: trabaja a 15-18 grados C con 50-60 % de humedad, y es lo que sostiene la cristalización y la vida útil que declares en tu APPCC.</t>
+          <t>Aquí el «ciclo» es una rotación de la cámara. NO es una nevera: trabaja a 15-18 °C con 50-60 % de humedad, y es lo que sostiene la cristalización y la vida útil que declares en tu APPCC.</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>m2 de exposición por reposición</t>
+          <t>m² de exposición por reposición</t>
         </is>
       </c>
       <c r="G15" s="8" t="n">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>Rango de trabajo del equipo +14/+17 grados C. NO son los +2/+4 de una vitrina de pastelería, que arruina el bombón por condensación y pérdida de brillo. El objetivo operativo de cada mañana lo pone el kit: 16-18 grados C y menos del 55 % de humedad.</t>
+          <t>Rango de trabajo del equipo +14/+17 °C. NO son los +2/+4 de una vitrina de pastelería, que arruina el bombón por condensación y pérdida de brillo. El objetivo operativo de cada mañana lo pone el kit: 16-18 °C y menos del 55 % de humedad.</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>ES LA ELIMINATORIA PROPIA DE UNA CHOCOLATERÍA. Sin 18-20 grados C y 50-60 % de humedad en el obrador, la cobertura no cristaliza y el bombón sale mate o con fat bloom. Un local que no se puede climatizar no es un local barato: es otro negocio.</t>
+          <t>ES LA ELIMINATORIA PROPIA DE UNA CHOCOLATERÍA. Sin 18-20 °C y 50-60 % de humedad en el obrador, la cobertura no cristaliza y el bombón sale mate o con fat bloom. Un local que no se puede climatizar no es un local barato: es otro negocio.</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>La superficie útil llega a los m2 que has repartido por zonas</t>
+          <t>La superficie útil llega a los m² que has repartido por zonas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Superficie útil real, sin contar muros ni patinillos. Compárala con el total de la hoja «Zonas y m2».</t>
+          <t>Superficie útil real, sin contar muros ni patinillos. Compárala con el total de la hoja «Zonas y m²».</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>La superficie de un anuncio suele ser construida. La que te sirve es la útil, y entre una y otra se van con facilidad 10 m2.</t>
+          <t>La superficie de un anuncio suele ser construida. La que te sirve es la útil, y entre una y otra se van con facilidad 10 m².</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Mide sólo la zona a la que entra el público. La de la hoja «Zonas y m2» es la de partida.</t>
+          <t>Mide sólo la zona a la que entra el público. La de la hoja «Zonas y m²» es la de partida.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Por debajo de 750 m2 de superficie útil de exposición y venta al público, ninguna administración puede exigirte licencia previa de instalación, de funcionamiento o de actividad: el epígrafe 644.5 está en el Anexo de la Ley 12/2012. Decir qué trámite pide Madrid o Barcelona está PROHIBIDO en esta guía: no se ha abierto ninguna ordenanza.</t>
+          <t>Por debajo de 750 m² de superficie útil de exposición y venta al público, ninguna administración puede exigirte licencia previa de instalación, de funcionamiento o de actividad: el epígrafe 644.5 está en el Anexo de la Ley 12/2012. Decir qué trámite pide Madrid o Barcelona está PROHIBIDO en esta guía: no se ha abierto ninguna ordenanza.</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>La chocolatería de TAZA es otro negocio y la norma lo separa sola: el Anexo de la Ley 12/2012 NO incluye ningún grupo de la agrupación 67, así que la bombonería se libra de la licencia previa hasta 750 m2 y la de taza no. Y si hay freidora de gas, la instalación receptora se inspecciona cada cinco años.</t>
+          <t>La chocolatería de TAZA es otro negocio y la norma lo separa sola: el Anexo de la Ley 12/2012 NO incluye ningún grupo de la agrupación 67, así que la bombonería se libra de la licencia previa hasta 750 m² y la de taza no. Y si hay freidora de gas, la instalación receptora se inspecciona cada cinco años.</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>El personal necesita su aseo y su taquilla; el cliente, el suyo. Los 8 m2 de la hoja de zonas ya lo contemplan.</t>
+          <t>El personal necesita su aseo y su taquilla; el cliente, el suyo. Los 8 m² de la hoja de zonas ya lo contemplan.</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>La vitrina de bombonería trabaja a 16-18 grados C. Un escaparate a poniente en julio la obliga a ciclar sin parar, sube la humedad interior y te deja el bombón mate. Se arregla con lámina solar y toldo, que son partida del libro 2, pero hay que saberlo antes.</t>
+          <t>La vitrina de bombonería trabaja a 16-18 °C. Un escaparate a poniente en julio la obliga a ciclar sin parar, sube la humedad interior y te deja el bombón mate. Se arregla con lámina solar y toldo, que son partida del libro 2, pero hay que saberlo antes.</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
     <row r="42" ht="62" customHeight="1">
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>LA DIFERENCIA CON UNA PASTELERÍA CABE EN DOS LÍNEAS DE ESTA FICHA. Un obrador de chocolate no fríe ni asa, así que no necesita campana ni conducto a cubierta: se cae la partida que tumba la mitad de los locales. A cambio aparece otra que en pastelería no existe, y es eliminatoria: el local tiene que poder climatizarse con deshumidificación a 18-20 grados C. Un sótano fresco y húmedo es un mal local para el chocolate aunque esté regalado.</t>
+          <t>LA DIFERENCIA CON UNA PASTELERÍA CABE EN DOS LÍNEAS DE ESTA FICHA. Un obrador de chocolate no fríe ni asa, así que no necesita campana ni conducto a cubierta: se cae la partida que tumba la mitad de los locales. A cambio aparece otra que en pastelería no existe, y es eliminatoria: el local tiene que poder climatizarse con deshumidificación a 18-20 °C. Un sótano fresco y húmedo es un mal local para el chocolate aunque esté regalado.</t>
         </is>
       </c>
     </row>

--- a/scripts/productos-digitales/guia-chocolateria/build/capacidad-obrador-y-clima.xlsx
+++ b/scripts/productos-digitales/guia-chocolateria/build/capacidad-obrador-y-clima.xlsx
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>grados C</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>grados C</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Es la tarea 17 de la hoja, y es el objetivo mas restrictivo que publica el kit: es el que manda. `CHS-44` publica 18-22 °C como rango de trabajo de un tercero, y entra en la prosa del cap. 07 como tal, nunca como objetivo del juego de datos.</t>
+          <t>Es la tarea 17 de la hoja, y es el objetivo más restrictivo que publica el kit: es el que manda. `CHS-44` publica 18-22 °C como rango de trabajo de un tercero, y entra en la prosa del cap. 07 como tal, nunca como objetivo del juego de datos.</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Comprobar que las vitrinas temperadas han alcanzado 16-18 °C y menos del 55 % de humedad antes de montar el genero</t>
+          <t>Comprobar que las vitrinas temperadas han alcanzado 16-18 °C y menos del 55 % de humedad antes de montar el género</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>grados C</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>El corazón del obrador, la decisión 2 del bonus 2 y la máquina que más se mira al presupuestar. Fíjate en dónde queda en el cuello de botella: templar NO es lo que limita una bombonería artesana. Los bombones por kilo salen de los 5,5 g de chocolate de la tanda de referencia; cámbialos si tu pieza pesa otra cosa.</t>
+          <t>El corazón del obrador, la decisión 2 del bonus 2 y la máquina que más se mira al presupuestar. Fíjate en dónde queda en el cuello de botella: templar NO es lo que limita una bombonería artesana. Los bombones por kilo salen de los 5,5 g de chocolate de la tanda de referencia; cámbialos si tu pieza pesa otra cosa. Los 180 minutos NO son el rendimiento de su ficha (55 kg/h): son el ritmo al que el obrador vacía la cuba sobre el moldeado, con carga, templado, vaciado y cristalización. Por eso esta columna NO es comparable entre una máquina continua y una de lote: que la fila 16 (3 kg) dé más bombones al día que ésta (12 kg) es un efecto de cuántos ciclos enteros caben en los 408 minutos de la jornada, no una ventaja de la máquina pequeña.</t>
         </is>
       </c>
     </row>
